--- a/artfynd/A 54906-2022 artfynd.xlsx
+++ b/artfynd/A 54906-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54906-2022 artfynd.xlsx
+++ b/artfynd/A 54906-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2932,6 +2932,414 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118068272</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90499</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Persgårdsbodarna (Persgårdsbodarna), Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>506295</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7052054</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118068290</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90841</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Persgårdsbodarna (Persgårdsbodarna), Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>506295</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7052054</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118068010</v>
+      </c>
+      <c r="B22" t="n">
+        <v>96869</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Persgårdsbodarna (Persgårdsbodarna), Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>506403</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7052026</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118070666</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98430</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>256</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Finnstarr</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carex atherodes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Spreng.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Persgårdsbodarna (Persgårdsbodarna), Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>506100</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7052474</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Fredrik Larsson, Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54906-2022 artfynd.xlsx
+++ b/artfynd/A 54906-2022 artfynd.xlsx
@@ -3036,10 +3036,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118068290</v>
+        <v>118070666</v>
       </c>
       <c r="B21" t="n">
-        <v>90841</v>
+        <v>98430</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3052,21 +3052,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>256</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Finnstarr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Carex atherodes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Spreng.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506295</v>
+        <v>506100</v>
       </c>
       <c r="R21" t="n">
-        <v>7052054</v>
+        <v>7052474</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118068010</v>
+        <v>118068290</v>
       </c>
       <c r="B22" t="n">
-        <v>96869</v>
+        <v>90841</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3150,25 +3150,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222112</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506403</v>
+        <v>506295</v>
       </c>
       <c r="R22" t="n">
-        <v>7052026</v>
+        <v>7052054</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3240,10 +3240,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118070666</v>
+        <v>118068010</v>
       </c>
       <c r="B23" t="n">
-        <v>98430</v>
+        <v>96869</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3252,25 +3252,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>256</v>
+        <v>222112</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finnstarr</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carex atherodes</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Spreng.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506100</v>
+        <v>506403</v>
       </c>
       <c r="R23" t="n">
-        <v>7052474</v>
+        <v>7052026</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 54906-2022 artfynd.xlsx
+++ b/artfynd/A 54906-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2937,7 +2937,7 @@
         <v>118068272</v>
       </c>
       <c r="B20" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118070666</v>
+        <v>118068010</v>
       </c>
       <c r="B21" t="n">
-        <v>98430</v>
+        <v>96871</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3048,25 +3048,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>256</v>
+        <v>222112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Finnstarr</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carex atherodes</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Spreng.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506100</v>
+        <v>506403</v>
       </c>
       <c r="R21" t="n">
-        <v>7052474</v>
+        <v>7052026</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3141,7 +3141,7 @@
         <v>118068290</v>
       </c>
       <c r="B22" t="n">
-        <v>90841</v>
+        <v>90843</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3237,108 +3237,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>118068010</v>
-      </c>
-      <c r="B23" t="n">
-        <v>96869</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>222112</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Månlåsbräken</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Botrychium lunaria</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Persgårdsbodarna (Persgårdsbodarna), Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>506403</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7052026</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim, Fredrik Larsson, Jonny Daborg</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
